--- a/FAIR_instructions_with_prompts_and_answers1.xlsx
+++ b/FAIR_instructions_with_prompts_and_answers1.xlsx
@@ -519,24 +519,28 @@
 - If yes, data sharing consent: All research participants will be consented for broad data sharing.
 - Data to be collected: Demographic, clinical, and MRI, 1 H fMRS and fMRI imaging data will be acquired from 110 affected youth and 110 matched healthy controls (described in detail in sections C.3 and C.4 of this application). All data will be deidentified prior to receipt by the repository, but the information needed to generate a global unique identifier for the NIMH Data Archive (NDA) will be collected for each subject.
 Based on these inputs, provide clear, practical, and user-friendly FAIR data guidance organized under the following sections:
-1. Recommended file formats  
-Explain which file format(s) should be used for this type of data and why they are appropriate for FAIR sharing and reuse.
-2. Relevant tools and software  
-List tools, software, or platforms that can help prepare, convert, validate, organize, document, or share this type of data.
-3. Recommended dataset structure or standard  
-State the dataset structure, schema, or community standard that should be followed, if one exists.
-4. Dataset organization details  
-Provide detailed guidance on how the dataset should be organized, including folder structure, file naming conventions, table organization, metadata arrangement, versioning considerations, and any other important technical details.
-5. Metadata and documentation files to include  
-List the metadata files, README files, data dictionaries, codebooks, protocols, or other documentation that should accompany the dataset.
-6. Tools for metadata preparation and validation  
-Suggest tools that can help create, validate, manage, or standardize metadata for this dataset.
-7. De-identification and privacy considerations  
-State whether de-identification is required. Explain what should be done based on the subject type, the data modality, and whether the study involves human participants. If consent language affects sharing, explain that clearly.
-8. Recommended repositories  
-Suggest appropriate repositories for sharing the data, prioritizing repositories recommended, required, or commonly accepted by the funding source and data type.
-9. Recommended data licenses  
-Recommend appropriate data license(s), prioritizing those expected, suggested, or required by the funding source. If restrictions apply because of human subjects or consent limitations, explain that clearly.
+1- Suggested file formats for each data type
+Identify the recommended file format or formats for each data type in the dataset. Briefly explain why these formats are appropriate for FAIR sharing, reuse, interoperability, and long-term preservation.
+2- Tools for converting data to the suggested file formats
+List tools, software, or workflows that can be used to convert raw or source data into the recommended file formats.
+3- Suggested standard structure to organize the dataset
+State the recommended dataset structure, schema, specification, or community standard that should be used to organize the dataset, if one exists.
+4- Tools for organizing the dataset in the suggested structure
+List tools, software, templates, or platforms that can help organize the dataset according to the recommended structure or standard.
+5- Metadata and information that should be provided with the data
+Describe the metadata, documentation, contextual information, data dictionaries, codebooks, README files, protocols, and any other supporting information that should accompany the dataset.
+6- Suggested standard structure and file format for metadata
+State the recommended structure, schema, standard, and file format that should be used for metadata and documentation files included with the dataset.
+7-Tools for preparing metadata in the suggested structure and file format
+List tools, software, validators, templates, or platforms that can help create, manage, standardize, or validate metadata in the recommended structure and format.
+8- Suggested de-identification approach
+State whether de-identification is required. Explain the recommended de-identification or privacy-preserving approach based on the subject type, data modality, sensitivity of the data, and whether human participants are involved. If consent language affects sharing, explain that clearly.
+9- Tools to implement the suggested de-identification approach
+List tools, software, workflows, or methods that can help implement the recommended de-identification or privacy protection approach.
+10-Suggested repositories for sharing the dataset
+Recommend appropriate repositories for sharing the dataset, prioritizing repositories required, recommended, or commonly accepted by the funding source, subject type, and data modality.
+11- Suggested license for sharing the dataset
+Recommend an appropriate data license or licensing approach, prioritizing what is expected, suggested, or required by the funding source. If restrictions apply because of human subjects, controlled access, or consent limitations, explain that clearly.
 Instructions for your response:
 - Make the guidance practical, concise, and easy for researchers to follow.
 - Tailor all recommendations to the combination of funding source, human-subject status, consent language, and data modality.
@@ -548,109 +552,86 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>**FAIR Data Guidance for NIH/NIMH Human Subjects Imaging Study**
----
-### 1. Recommended File Formats
-- **Demographic &amp; Clinical Data:**  
-  Use **CSV** (Comma-Separated Values) or **TSV** (Tab-Separated Values) for tabular data. These are open, non-proprietary, and widely supported formats that facilitate reuse and interoperability.
-- **MRI, fMRI, and 1H fMRS Imaging Data:**  
-  Use **NIfTI (.nii or .nii.gz)** for MRI and fMRI data. For raw scanner data, **DICOM** is acceptable, but NIfTI is preferred for sharing and analysis.  
-  For spectroscopy (fMRS), use **NIfTI-MRS** or **vendor-neutral formats** (e.g., LCModel .RAW, .SDAT, or .SPAR), with conversion to NIfTI-MRS if possible.
-- **Documentation &amp; Metadata:**  
-  Use **PDF** or **Markdown (.md)** for protocols and README files. Use **JSON** or **TSV** for structured metadata (e.g., BIDS sidecar files).
----
-### 2. Relevant Tools and Software
-- **Data Conversion &amp; Organization:**  
-  - [dcm2niix](https://github.com/rordenlab/dcm2niix): DICOM to NIfTI conversion  
-  - [BIDScoin](https://bidscoin.readthedocs.io/): Automated BIDS conversion  
-  - [HeuDiConv](https://heudiconv.readthedocs.io/): DICOM to BIDS conversion
-- **Validation:**  
-  - [BIDS Validator](https://bids-standard.github.io/bids-validator/): Checks BIDS compliance  
-  - [NDA Validation Tools](https://nda.nih.gov/nda/tools/): For NDA-specific requirements
-- **Data Management:**  
-  - [REDCap](https://www.project-redcap.org/): For clinical/demographic data collection  
-  - [OpenRefine](https://openrefine.org/): Data cleaning and standardization
----
-### 3. Recommended Dataset Structure or Standard
+          <t>Certainly! Below is practical, NIH/NIMH-tailored FAIR data guidance for your grant proposal, based on your study context.
+---
+## 1. Suggested file formats for each data type
+**Demographic &amp; Clinical Data:**  
+- **Format:** CSV (.csv), TSV (.tsv), or JSON (.json)  
+- **Rationale:** These are open, non-proprietary, widely supported formats that facilitate interoperability, reuse, and long-term preservation.
+**MRI, 1H fMRS, and fMRI Imaging Data:**  
+- **Format:** NIfTI (.nii or .nii.gz) for image data; DICOM (.dcm) for raw data  
+- **Rationale:** NIfTI is the community standard for neuroimaging, supported by most analysis tools and repositories. DICOM is the clinical acquisition standard but should be converted to NIfTI for sharing and analysis.
+---
+## 2. Tools for converting data to the suggested file formats
+- **Demographic/Clinical Data:**  
+  - Microsoft Excel, LibreOffice Calc, R, or Python (pandas) for exporting to CSV/TSV/JSON.
 - **Imaging Data:**  
-  Follow the **Brain Imaging Data Structure (BIDS)** standard (https://bids.neuroimaging.io/), including BIDS extensions for fMRI and MRS data.
-- **Clinical/Demographic Data:**  
-  Organize as BIDS-compliant tabular files (e.g., `participants.tsv`, `phenotype/` folder).
-- **Metadata:**  
-  Use BIDS sidecar JSON files for imaging metadata and NDA-required data dictionaries for tabular data.
----
-### 4. Dataset Organization Details
-- **Folder Structure:**  
-  ```
-  /project_root/
-      /sub-&lt;participant_label&gt;/
-          /anat/         # Structural MRI
-          /func/         # fMRI
-          /mrs/          # fMRS
-      /phenotype/        # Clinical/demographic data
-      participants.tsv   # Participant-level summary
-      dataset_description.json  # BIDS metadata
-      README.md
-      CHANGES.md         # Version history
-      /code/             # Analysis scripts (if applicable)
-  ```
-- **File Naming Conventions:**  
-  Use BIDS conventions: `sub-&lt;participant_label&gt;_ses-&lt;session&gt;_task-&lt;task&gt;_modality.nii.gz`
-- **Table Organization:**  
-  - `participants.tsv`: One row per subject, columns for age, sex, group, etc.
-  - Data dictionaries: Define each variable, units, and allowed values.
-- **Metadata Arrangement:**  
-  - BIDS sidecar JSON files for each imaging file.
-  - NDA-specific data dictionaries and manifest files as required.
-- **Versioning:**  
-  - Maintain a `CHANGES.md` file.
-  - Use versioned folder names or tags for major dataset updates.
----
-### 5. Metadata and Documentation Files to Include
-- **README.md:** Overview of dataset, study design, and file organization.
-- **dataset_description.json:** BIDS-required metadata (title, authors, funding, references).
-- **participants.tsv:** Participant-level data.
-- **Data Dictionary:** Defines all variables in tabular data.
-- **Protocol Documents:** Study protocol, consent forms (de-identified), and data collection instruments.
-- **CHANGES.md:** Version history.
-- **NDA Submission Files:** As required by the NIMH Data Archive (e.g., manifest, data dictionary).
----
-### 6. Tools for Metadata Preparation and Validation
-- **BIDS Validator:** For checking BIDS compliance.
-- **NDA Data Dictionary Tool:** For preparing NDA-compliant data dictionaries.
-- **OpenRefine:** For cleaning and standardizing tabular metadata.
-- **BIDS Starter Kit:** Templates and guidance for BIDS metadata.
----
-### 7. De-identification and Privacy Considerations
-- **De-identification is required** for all human subjects data prior to sharing.
+  - [dcm2niix](https://github.com/rordenlab/dcm2niix): Converts DICOM to NIfTI.
+  - [MRIconvert](https://lcni.uoregon.edu/downloads/mriconvert): Alternative for DICOM to NIfTI conversion.
+---
+## 3. Suggested standard structure to organize the dataset
+- **Recommended Standard:** [BIDS (Brain Imaging Data Structure)](https://bids.neuroimaging.io/)  
+- **Rationale:** BIDS is the widely adopted community standard for organizing neuroimaging and associated behavioral/clinical data, required by many repositories (including NIMH Data Archive).
+---
+## 4. Tools for organizing the dataset in the suggested structure
+- [BIDS Starter Kit](https://github.com/bids-standard/bids-starter-kit): Templates and guides for BIDS organization.
+- [HeuDiConv](https://github.com/nipy/heudiconv): Automated DICOM-to-BIDS conversion.
+- [BIDScoin](https://bidscoin.readthedocs.io/): GUI tool for converting and organizing data into BIDS.
+- [OpenNeuro BIDS Validator](https://bids-standard.github.io/bids-validator/): Checks dataset compliance with BIDS.
+---
+## 5. Metadata and information that should be provided with the data
+- **README file:** Overview of the dataset, study design, and data collection protocols.
+- **Data dictionary/codebook:** Definitions and allowable values for all variables in demographic/clinical data.
+- **Dataset description:** Study aims, participant inclusion/exclusion criteria, and data acquisition details.
+- **Acquisition protocols:** Detailed MRI/fMRI/fMRS acquisition parameters.
+- **Consent documentation:** Template or summary of consent language permitting broad data sharing.
+- **Processing scripts:** Any code or workflow used for data preprocessing or analysis.
+---
+## 6. Suggested standard structure and file format for metadata
+- **Structure:** BIDS metadata files (sidecar JSON files for imaging data, dataset_description.json, participants.tsv, etc.)
+- **Format:** JSON (.json) for structured metadata; TSV (.tsv) for tabular data.
+- **Rationale:** BIDS-compliant metadata ensures interoperability and reusability, and is required by most neuroimaging repositories.
+---
+## 7. Tools for preparing metadata in the suggested structure and file format
+- [BIDS Starter Kit](https://github.com/bids-standard/bids-starter-kit): Metadata templates and examples.
+- [BIDS Validator](https://bids-standard.github.io/bids-validator/): Checks metadata completeness and correctness.
+- [OpenNeuro Metadata Editor](https://openneuro.org/): Online tool for editing BIDS metadata.
+- [BIDScoin](https://bidscoin.readthedocs.io/): Assists with metadata creation during conversion.
+---
+## 8. Suggested de-identification approach
+- **Requirement:** De-identification is required for all human subject data prior to sharing.
+- **Approach:**  
+  - Remove all direct identifiers (names, dates of birth, addresses, etc.).
+  - For imaging data, remove facial features from structural scans (defacing).
+  - Use the NIMH Data Archive (NDA) Global Unique Identifier (GUID) system to pseudonymize subjects.
+  - Retain only the minimum necessary demographic information (e.g., age at scan, sex, race/ethnicity as permitted by consent).
+- **Consent:** All participants are consented for broad data sharing, enabling data deposition in controlled-access repositories.
+---
+## 9. Tools to implement the suggested de-identification approach
 - **Imaging Data:**  
-  - Remove all facial features from structural MRI (defacing tools: [pydeface](https://github.com/poldracklab/pydeface), [mri_deface](https://surfer.nmr.mgh.harvard.edu/fswiki/mri_deface)).
-  - Strip all personal identifiers from DICOM headers.
-- **Tabular Data:**  
-  - Remove direct identifiers (names, dates of birth, addresses, etc.).
-  - Use NDA Global Unique Identifier (GUID) for subject linkage.
-- **Consent:**  
-  - All participants are consented for broad data sharing, enabling deposition in open or controlled-access repositories as required by NIH/NIMH.
-- **Documentation:**  
-  - Document de-identification procedures in the README or a dedicated file.
----
-### 8. Recommended Repositories
-- **Primary:**  
-  - **NIMH Data Archive (NDA):** Required for NIMH-funded human subjects data (https://nda.nih.gov/).
-- **Secondary (if allowed by NDA and consent):**  
-  - **OpenNeuro:** For BIDS-compliant imaging datasets (https://openneuro.org/).
-  - **Other NIH-supported repositories** as appropriate for specific data types.
----
-### 9. Recommended Data Licenses
-- **NDA:**  
-  - Data shared via NDA is governed by NDA’s Data Use Certification and access controls. No separate license is required; NDA policies apply.
-- **Open Repositories (if used):**  
-  - Use **CC BY 4.0** (Creative Commons Attribution) or **CC0** (public domain dedication) for de-identified data, unless participant consent or NDA policy restricts this.
-- **Human Subjects Considerations:**  
-  - Since broad sharing consent is obtained, open licenses are generally permissible, but always ensure compliance with NDA and NIH policies.
+  - [pydeface](https://github.com/poldracklab/pydeface), [mri_deface](https://surfer.nmr.mgh.harvard.edu/fswiki/mri_deface): For defacing MRI images.
+  - [dcm2niix](https://github.com/rordenlab/dcm2niix): Removes DICOM headers with PHI during conversion.
+- **Demographic/Clinical Data:**  
+  - Manual review and scripting (R, Python) to remove identifiers.
+- **NDA GUID Tool:**  
+  - [NDA GUID Tool](https://nda.nih.gov/tools.html): For generating and managing subject GUIDs.
+---
+## 10. Suggested repositories for sharing the dataset
+- **Primary Recommendation:** [NIMH Data Archive (NDA)](https://nda.nih.gov/)  
+  - **Rationale:** NDA is required for NIMH-funded human subjects research and supports controlled access, GUIDs, and BIDS datasets.
+- **Secondary/Complementary:**  
+  - [OpenNeuro](https://openneuro.org/): For open-access sharing of BIDS-compliant neuroimaging data (if appropriate and permitted by consent).
+  - [dbGaP](https://www.ncbi.nlm.nih.gov/gap): For genetic or sensitive clinical data, if applicable.
+---
+## 11. Suggested license for sharing the dataset
+- **Recommended License:**  
+  - **NDA:** Data are shared under NDA’s Data Use Certification Agreement, which provides controlled access and requires users to agree to terms of use.
+  - **OpenNeuro (if used):** [CC0 1.0 Universal (Public Domain Dedication)](https://creativecommons.org/publicdomain/zero/1.0/) is the default, but only if permitted by consent and IRB.
+- **Restrictions:**  
+  - Because data are from human subjects, sharing must comply with participant consent, IRB approval, and repository access controls. Broad sharing is permitted per your consent language, but controlled access via NDA is required by NIMH.
 ---
 **Summary:**  
-By following these recommendations—using open formats, BIDS structure, robust metadata, NDA submission requirements, and appropriate de-identification—your dataset will be well-aligned with FAIR principles and NIH/NIMH expectations for human subjects imaging research.</t>
+By following these recommendations—using open, community-accepted formats (CSV, NIfTI, BIDS), robust de-identification, comprehensive metadata, and depositing in the NIMH Data Archive with appropriate licensing—you will maximize the FAIRness, impact, and compliance of your dataset.</t>
         </is>
       </c>
     </row>
@@ -702,24 +683,28 @@
  will be submitted to the NIMH Data Archive (NDA). Phenotypic and clinical data for all 500 research subjects will 
  be collected and deposited in NDA using the data dictionaries available in NDA (described below).
 Based on these inputs, provide clear, practical, and user-friendly FAIR data guidance organized under the following sections:
-1. Recommended file formats  
-Explain which file format(s) should be used for this type of data and why they are appropriate for FAIR sharing and reuse.
-2. Relevant tools and software  
-List tools, software, or platforms that can help prepare, convert, validate, organize, document, or share this type of data.
-3. Recommended dataset structure or standard  
-State the dataset structure, schema, or community standard that should be followed, if one exists.
-4. Dataset organization details  
-Provide detailed guidance on how the dataset should be organized, including folder structure, file naming conventions, table organization, metadata arrangement, versioning considerations, and any other important technical details.
-5. Metadata and documentation files to include  
-List the metadata files, README files, data dictionaries, codebooks, protocols, or other documentation that should accompany the dataset.
-6. Tools for metadata preparation and validation  
-Suggest tools that can help create, validate, manage, or standardize metadata for this dataset.
-7. De-identification and privacy considerations  
-State whether de-identification is required. Explain what should be done based on the subject type, the data modality, and whether the study involves human participants. If consent language affects sharing, explain that clearly.
-8. Recommended repositories  
-Suggest appropriate repositories for sharing the data, prioritizing repositories recommended, required, or commonly accepted by the funding source and data type.
-9. Recommended data licenses  
-Recommend appropriate data license(s), prioritizing those expected, suggested, or required by the funding source. If restrictions apply because of human subjects or consent limitations, explain that clearly.
+1- Suggested file formats for each data type
+Identify the recommended file format or formats for each data type in the dataset. Briefly explain why these formats are appropriate for FAIR sharing, reuse, interoperability, and long-term preservation.
+2- Tools for converting data to the suggested file formats
+List tools, software, or workflows that can be used to convert raw or source data into the recommended file formats.
+3- Suggested standard structure to organize the dataset
+State the recommended dataset structure, schema, specification, or community standard that should be used to organize the dataset, if one exists.
+4- Tools for organizing the dataset in the suggested structure
+List tools, software, templates, or platforms that can help organize the dataset according to the recommended structure or standard.
+5- Metadata and information that should be provided with the data
+Describe the metadata, documentation, contextual information, data dictionaries, codebooks, README files, protocols, and any other supporting information that should accompany the dataset.
+6- Suggested standard structure and file format for metadata
+State the recommended structure, schema, standard, and file format that should be used for metadata and documentation files included with the dataset.
+7-Tools for preparing metadata in the suggested structure and file format
+List tools, software, validators, templates, or platforms that can help create, manage, standardize, or validate metadata in the recommended structure and format.
+8- Suggested de-identification approach
+State whether de-identification is required. Explain the recommended de-identification or privacy-preserving approach based on the subject type, data modality, sensitivity of the data, and whether human participants are involved. If consent language affects sharing, explain that clearly.
+9- Tools to implement the suggested de-identification approach
+List tools, software, workflows, or methods that can help implement the recommended de-identification or privacy protection approach.
+10-Suggested repositories for sharing the dataset
+Recommend appropriate repositories for sharing the dataset, prioritizing repositories required, recommended, or commonly accepted by the funding source, subject type, and data modality.
+11- Suggested license for sharing the dataset
+Recommend an appropriate data license or licensing approach, prioritizing what is expected, suggested, or required by the funding source. If restrictions apply because of human subjects, controlled access, or consent limitations, explain that clearly.
 Instructions for your response:
 - Make the guidance practical, concise, and easy for researchers to follow.
 - Tailor all recommendations to the combination of funding source, human-subject status, consent language, and data modality.
@@ -733,93 +718,105 @@
         <is>
           <t>Certainly! Below is practical, NIH/NIMH-tailored FAIR data guidance for your human subjects genomic study, organized by the requested sections.
 ---
-### 1. Recommended File Formats
-**Genomic Data:**
-- **Raw sequencing data:** Use **FASTQ** format for raw reads; **BAM/CRAM** for aligned reads; **VCF** for variant calls. These are community standards, widely supported, and required by dbGaP and NDA.
-- **Phenotypic/clinical data:** Use **CSV** or **TSV** (plain text, comma/tab-delimited) for tabular data. These formats are non-proprietary, machine-readable, and facilitate reuse.
-- **Metadata and documentation:** Use **JSON**, **XML**, or **TXT** for structured metadata; **PDF** or **TXT** for protocols and README files.
-### 2. Relevant Tools and Software
-- **Data preparation/conversion:**  
-  - **SAMtools** (BAM/CRAM handling), **bcftools** (VCF), **PLINK** (genotype data), **seqtk** (FASTQ manipulation)
-- **Validation:**  
-  - **NDA Validation Tool** (for NDA submissions), **dbGaP Submission Portal** (for dbGaP)
-- **Organization/documentation:**  
-  - **Excel** or **Google Sheets** (for initial tabular data, export as CSV/TSV), **OpenRefine** (data cleaning)
-- **Metadata management:**  
-  - **NDA Data Dictionary Tool**, **ISA-Tab tools** (for multi-omics metadata structuring)
-### 3. Recommended Dataset Structure or Standard
-- **Genomic data:** Follow **dbGaP** and **NDA** submission guidelines for file structure and metadata.
-- **Phenotypic/clinical data:** Use **NDA Data Dictionary** standards, mapping variables to NDA-defined elements.
-- **Metadata:** Use **NDA’s structured metadata templates** and controlled vocabularies.
-### 4. Dataset Organization Details
-- **Folder structure:**  
-  ```
-  /project_root/
-      /raw_data/
-          /genomics/
-              sample1_R1.fastq.gz
-              sample1_R2.fastq.gz
-              ...
-          /phenotype/
-              phenotypic_data.csv
-      /processed_data/
-          sample1.bam
-          sample1.vcf
-          ...
-      /metadata/
-          NDA_submission_manifest.csv
-          data_dictionary.json
-          README.txt
-      /documentation/
-          consent_form_template.pdf
-          protocols.pdf
-  ```
-- **File naming conventions:**  
-  - Use unique, consistent IDs (e.g., `subjectID_sampleID_date.filetype`).
-  - Avoid spaces/special characters; use underscores or hyphens.
-- **Table organization:**  
-  - One row per subject/sample; columns for variables, using NDA variable names.
-- **Metadata arrangement:**  
-  - Store metadata files in a dedicated `/metadata/` folder.
-- **Versioning:**  
-  - Use version numbers in filenames (e.g., `phenotypic_data_v1.csv`).
-  - Maintain a changelog in the README.
-### 5. Metadata and Documentation Files to Include
-- **README.txt:** Overview of dataset, structure, and file descriptions.
-- **Data dictionary:** Define each variable, units, allowed values, and NDA mapping.
-- **Submission manifest:** Required by NDA/dbGaP, listing files and metadata.
-- **Consent form template:** Document participant consent for broad data sharing.
-- **Protocols:** Detailed data collection and processing protocols.
-- **Codebooks:** For any coded variables.
-- **Data processing scripts:** If applicable, include scripts or workflow descriptions.
-### 6. Tools for Metadata Preparation and Validation
-- **NDA Data Dictionary Tool:** For creating and validating data dictionaries.
-- **NDA Validation Tool:** Checks data and metadata compliance before submission.
-- **dbGaP Submission Portal:** For metadata entry and validation.
-- **ISA-Tab tools:** For multi-omics metadata structuring (if needed).
-### 7. De-identification and Privacy Considerations
+### 1. Suggested file formats for each data type
+**a. Raw Whole Genome Sequencing Data:**  
+- **Format:** FASTQ (raw reads), BAM/CRAM (aligned reads), VCF (variant calls)  
+- **Rationale:** These are community-standard, open formats widely supported by genomics tools and repositories. They ensure interoperability, long-term preservation, and broad reuse.
+**b. Derived Genomic Data (e.g., variant annotations):**  
+- **Format:** VCF (for variants), TSV/CSV (for tabular annotations)  
+- **Rationale:** VCF is the standard for variant data; TSV/CSV are open, machine-readable, and widely supported.
+**c. Phenotypic and Clinical Data:**  
+- **Format:** CSV/TSV (tabular data), following NDA data dictionary templates  
+- **Rationale:** CSV/TSV are open, non-proprietary, and compatible with NDA requirements.
+**d. Metadata and Documentation:**  
+- **Format:** JSON, XML, or CSV (for structured metadata); PDF or TXT (for protocols, README)  
+- **Rationale:** JSON/XML are machine-readable and align with NDA and dbGaP metadata standards; PDF/TXT are accessible for human-readable documentation.
+---
+### 2. Tools for converting data to the suggested file formats
+- **FASTQ/BAM/CRAM/VCF:**  
+  - [samtools](http://www.htslib.org/), [bcftools](http://www.htslib.org/), [GATK](https://gatk.broadinstitute.org/), [Picard](https://broadinstitute.github.io/picard/)
+- **CSV/TSV:**  
+  - Microsoft Excel, LibreOffice Calc, R, Python (pandas), NDA Data Dictionary Templates
+- **JSON/XML:**  
+  - R, Python, [OpenRefine](https://openrefine.org/), NDA Data Dictionary Tools
+- **PDF/TXT:**  
+  - Microsoft Word, Google Docs, LaTeX, Notepad
+---
+### 3. Suggested standard structure to organize the dataset
+- **Genomic Data:**  
+  - Organize by subject/sample ID, with subfolders for raw (FASTQ), aligned (BAM/CRAM), and variant (VCF) files.
+- **Phenotypic/Clinical Data:**  
+  - Use NDA data dictionary structure: one row per subject, columns as per NDA variable definitions.
+- **Metadata/Documentation:**  
+  - Include a top-level `README.txt`, data dictionaries, and protocol files.
+- **Recommended Standard:**  
+  - Follow the [NIMH Data Archive (NDA) Submission Structure](https://nda.nih.gov/nda/tools/submission.html) and [dbGaP Submission Guidelines](https://www.ncbi.nlm.nih.gov/gap/docs/submissionguide/).
+---
+### 4. Tools for organizing the dataset in the suggested structure
+- **NDA Data Submission Tool** (for uploading and structuring data per NDA requirements)
+- **dbGaP Submission Portal** (for genomic data registration)
+- **NDA Data Dictionary Templates** (Excel/CSV templates)
+- **File organization scripts** (custom scripts in Python/R for file/folder management)
+---
+### 5. Metadata and information that should be provided with the data
+- **Project-level metadata:** Study title, abstract, PI, funding source, IRB protocol, consent language
+- **Subject/sample metadata:** Unique IDs, demographic variables, consent group, collection site
+- **Data dictionaries:** Definitions, permissible values, units for each variable (use NDA templates)
+- **README file:** Overview of dataset structure, file descriptions, processing steps, contact info
+- **Protocols:** Detailed methods for sample collection, sequencing, data processing, QC
+- **Data provenance:** Software versions, pipeline parameters, date of data generation
+---
+### 6. Suggested standard structure and file format for metadata
+- **Structure:**  
+  - Use the [NDA Data Dictionary](https://nda.nih.gov/nda/data-dictionary.html) for phenotypic/clinical data
+  - Use [dbGaP metadata templates](https://www.ncbi.nlm.nih.gov/gap/docs/submissionguide/#metadata) for genomic data
+- **File formats:**  
+  - CSV/TSV for data dictionaries  
+  - JSON/XML for structured metadata (if required by repository)  
+  - PDF/TXT for protocols and README
+---
+### 7. Tools for preparing metadata in the suggested structure and file format
+- **NDA Data Dictionary Tool** (Excel/CSV templates and online validator)
+- **dbGaP Submission Portal** (metadata templates and validation)
+- **OpenRefine** (for cleaning and standardizing tabular metadata)
+- **R/Python scripts** (for generating JSON/XML metadata)
+- **NDA Validator** (for checking compliance with NDA requirements)
+---
+### 8. Suggested de-identification approach
 - **De-identification is required** for all human subjects data prior to sharing.
-- **Remove all direct identifiers** (names, addresses, contact info, etc.).
-- **Use NDA Global Unique Identifiers (GUIDs)** for subject IDs.
-- **Genomic data:** Ensure no identifying information is embedded in file headers or metadata.
-- **Consent:** Since participants are consented for broad data sharing, data can be shared via controlled-access repositories (dbGaP, NDA) in accordance with NIH policy.
-- **Review NDA and dbGaP de-identification guidance** to ensure compliance.
-### 8. Recommended Repositories
+- **Recommended approach:**  
+  - Remove all direct identifiers (names, addresses, contact info, etc.)
+  - Replace subject IDs with NDA Global Unique Identifiers (GUIDs)
+  - Generalize or bin sensitive indirect identifiers (e.g., age as age group)
+  - For genomic data, follow dbGaP/NDA guidelines for controlled-access and privacy protection
+- **Consent language:**  
+  - As all participants are consented for broad data sharing, data can be shared under controlled access, but must still be de-identified per NIH policy.
+---
+### 9. Tools to implement the suggested de-identification approach
+- **NDA GUID Tool** (for generating de-identified subject IDs)
+- **NDA Data Submission Tool** (flags identifiers and checks compliance)
+- **dbGaP Submission Portal** (guidance and checks for de-identification)
+- **Custom scripts** (for removing or generalizing indirect identifiers in tabular data)
+- **HIPAA Safe Harbor checklists** (for ensuring removal of 18 identifiers)
+---
+### 10. Suggested repositories for sharing the dataset
 - **Raw and processed genomic data:**  
-  - **dbGaP** (Database of Genotypes and Phenotypes) – NIH-required for human genomic data.
-  - **NIMH Data Archive (NDA):** Required for NIMH-funded studies; submit both genomic and phenotypic/clinical data.
-- **Phenotypic/clinical data:**  
-  - **NIMH Data Archive (NDA):** Use NDA data dictionaries and submission tools.
-### 9. Recommended Data Licenses
-- **Controlled-access data:**  
-  - Data in dbGaP and NDA are distributed under **NIH Data Use Certification Agreements**.  
-  - No open license (e.g., CC-BY) is permitted for human genomic data; access is restricted to qualified researchers with approved data use requests.
-- **Documentation and metadata:**  
-  - May be shared under **CC-BY 4.0** or similar open license, unless it contains sensitive information.
-**Note:** All data sharing must comply with participant consent and NIH/NIMH policies.
+  - [dbGaP (Database of Genotypes and Phenotypes)](https://www.ncbi.nlm.nih.gov/gap/) (required by NIH for human genomic data)
+- **Phenotypic and clinical data, derived data:**  
+  - [NIMH Data Archive (NDA)](https://nda.nih.gov/) (required by NIMH for mental health studies)
+- **Metadata and documentation:**  
+  - Included with submissions to dbGaP and NDA
+---
+### 11. Suggested license for sharing the dataset
+- **Controlled access license:**  
+  - Data will be shared under controlled access as required by NIH/NIMH for human genomic and sensitive clinical data.
+  - Users must apply for access and agree to data use limitations consistent with participant consent.
+- **Recommended approach:**  
+  - Specify “Data available under controlled access via dbGaP and NDA, subject to NIH Data Use Certification and participant consent restrictions.”
+  - Do **not** use open/public domain licenses (e.g., CC0) for human subjects data.
 ---
 **Summary:**  
-By following these recommendations, your data will be well-structured, compliant with NIH/NIMH requirements, and maximally FAIR—findable, accessible (via controlled access), interoperable, and reusable for the research community.</t>
+By following these recommendations, your dataset will be well-aligned with NIH/NIMH FAIR data expectations, maximize interoperability and reuse, and ensure compliance with privacy and consent requirements.</t>
         </is>
       </c>
     </row>
@@ -884,24 +881,28 @@
  The amount and type of data from human cells will depend on the results from the mouse studies. Data sharing 
  plans will be updated when appropriate (likely at the start of year 4 of the grant award).
 Based on these inputs, provide clear, practical, and user-friendly FAIR data guidance organized under the following sections:
-1. Recommended file formats  
-Explain which file format(s) should be used for this type of data and why they are appropriate for FAIR sharing and reuse.
-2. Relevant tools and software  
-List tools, software, or platforms that can help prepare, convert, validate, organize, document, or share this type of data.
-3. Recommended dataset structure or standard  
-State the dataset structure, schema, or community standard that should be followed, if one exists.
-4. Dataset organization details  
-Provide detailed guidance on how the dataset should be organized, including folder structure, file naming conventions, table organization, metadata arrangement, versioning considerations, and any other important technical details.
-5. Metadata and documentation files to include  
-List the metadata files, README files, data dictionaries, codebooks, protocols, or other documentation that should accompany the dataset.
-6. Tools for metadata preparation and validation  
-Suggest tools that can help create, validate, manage, or standardize metadata for this dataset.
-7. De-identification and privacy considerations  
-State whether de-identification is required. Explain what should be done based on the subject type, the data modality, and whether the study involves human participants. If consent language affects sharing, explain that clearly.
-8. Recommended repositories  
-Suggest appropriate repositories for sharing the data, prioritizing repositories recommended, required, or commonly accepted by the funding source and data type.
-9. Recommended data licenses  
-Recommend appropriate data license(s), prioritizing those expected, suggested, or required by the funding source. If restrictions apply because of human subjects or consent limitations, explain that clearly.
+1- Suggested file formats for each data type
+Identify the recommended file format or formats for each data type in the dataset. Briefly explain why these formats are appropriate for FAIR sharing, reuse, interoperability, and long-term preservation.
+2- Tools for converting data to the suggested file formats
+List tools, software, or workflows that can be used to convert raw or source data into the recommended file formats.
+3- Suggested standard structure to organize the dataset
+State the recommended dataset structure, schema, specification, or community standard that should be used to organize the dataset, if one exists.
+4- Tools for organizing the dataset in the suggested structure
+List tools, software, templates, or platforms that can help organize the dataset according to the recommended structure or standard.
+5- Metadata and information that should be provided with the data
+Describe the metadata, documentation, contextual information, data dictionaries, codebooks, README files, protocols, and any other supporting information that should accompany the dataset.
+6- Suggested standard structure and file format for metadata
+State the recommended structure, schema, standard, and file format that should be used for metadata and documentation files included with the dataset.
+7-Tools for preparing metadata in the suggested structure and file format
+List tools, software, validators, templates, or platforms that can help create, manage, standardize, or validate metadata in the recommended structure and format.
+8- Suggested de-identification approach
+State whether de-identification is required. Explain the recommended de-identification or privacy-preserving approach based on the subject type, data modality, sensitivity of the data, and whether human participants are involved. If consent language affects sharing, explain that clearly.
+9- Tools to implement the suggested de-identification approach
+List tools, software, workflows, or methods that can help implement the recommended de-identification or privacy protection approach.
+10-Suggested repositories for sharing the dataset
+Recommend appropriate repositories for sharing the dataset, prioritizing repositories required, recommended, or commonly accepted by the funding source, subject type, and data modality.
+11- Suggested license for sharing the dataset
+Recommend an appropriate data license or licensing approach, prioritizing what is expected, suggested, or required by the funding source. If restrictions apply because of human subjects, controlled access, or consent limitations, explain that clearly.
 Instructions for your response:
 - Make the guidance practical, concise, and easy for researchers to follow.
 - Tailor all recommendations to the combination of funding source, human-subject status, consent language, and data modality.
@@ -913,111 +914,123 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>**FAIR Data Guidance for Spatially Mapped Single-Cell Atlas of the Developing Mouse Brain (NIMH/NIH, Non-Human Subjects)**
----
-### 1. Recommended File Formats
-- **Primary data matrices**:  
-  - Use **HDF5-based formats** (e.g., `.h5ad` for AnnData, `.loom`, or `.h5` for 10x Genomics outputs) for large, multi-modal single-cell data. These formats are efficient, scalable, and widely supported.
-  - For smaller or tabular data, use **plain text formats**:  
-    - **CSV** (`.csv`) or **TSV** (`.tsv`) for count matrices and metadata tables.
-- **Metadata and documentation**:  
-  - Use **YAML** (`.yaml`), **JSON** (`.json`), or **CSV** for structured metadata.
-  - Use **plain text** (`.txt`) or **Markdown** (`.md`) for README and protocol files.
-**Rationale:**  
-These formats are open, non-proprietary, and supported by major analysis tools, facilitating interoperability and reuse.
----
-### 2. Relevant Tools and Software
-- **Data preparation and conversion**:  
-  - [Scanpy](https://scanpy.readthedocs.io/) (Python)  
-  - [Seurat](https://satijalab.org/seurat/) (R)  
-  - [Cell Ranger](https://support.10xgenomics.com/) (10x Genomics data processing)
-- **Data validation and organization**:  
-  - [Anndata](https://anndata.readthedocs.io/) (for `.h5ad` files)  
-  - [Loompy](http://loompy.org/) (for `.loom` files)
-- **Metadata management**:  
-  - [ISA-Tab tools](https://isa-tools.org/)  
-  - [DataLad](https://www.datalad.org/) (for versioning and organization)
-- **Data sharing**:  
-  - [Synapse](https://www.synapse.org/)  
-  - [Gene Expression Omnibus (GEO)](https://www.ncbi.nlm.nih.gov/geo/)  
-  - [NeMO Archive](https://nemoarchive.org/) (for neuroscience multi-omic data)
----
-### 3. Recommended Dataset Structure or Standard
-- **Recommended approach:**  
-  - Follow the **Open Biological and Biomedical Ontology (OBO) Foundry** standards for cell types and anatomical terms.
-  - Use the **AnnData** schema (as implemented in `.h5ad` files) for single-cell data, which is widely adopted in the community.
-  - For spatial data, consider the **SpaceTx Format** or **OME-NGFF** for imaging/spatial coordinates.
-  - For metadata, align with the **Minimum Information About a Single Cell Experiment (MINISEQE)** and **NIMH Data Archive (NDA) Common Data Elements** where applicable.
----
-### 4. Dataset Organization Details
-- **Folder structure:**  
-  ```
-  /project_root/
-    /raw_data/
-    /processed_data/
-    /metadata/
-    /docs/
-    /code/
-  ```
-- **File naming conventions:**  
-  - Use descriptive, consistent names:  
-    - `modality_species_timepoint_[other_details].h5ad` (e.g., `rna_mouse_E14_punch1.h5ad`)
-    - `metadata_cells_[date].csv`
-    - `README.md`, `data_dictionary.csv`, `protocols.md`
-- **Table organization:**  
-  - **Count matrices**: Rows = cells, Columns = features (genes, peaks, etc.)
-  - **Metadata tables**: One row per cell, columns for all metadata fields (sex, time point, punch coordinates, QC metrics, etc.)
-- **Versioning:**  
-  - Use semantic versioning (e.g., `v1.0`, `v1.1`) and maintain a `CHANGELOG.md`.
-  - Archive previous versions in a `/versions/` subfolder or via repository versioning.
-- **Other details:**  
-  - Ensure all files are UTF-8 encoded.
-  - Include checksums (e.g., `SHA256SUMS.txt`) for data integrity.
----
-### 5. Metadata and Documentation Files to Include
-- **README.md**: Overview of the dataset, structure, and usage instructions.
-- **Data dictionary** (`data_dictionary.csv`): Definitions and allowable values for all metadata fields.
-- **Protocols** (`protocols.md` or `.pdf`): Detailed experimental and data processing protocols.
-- **Metadata file** (`metadata_cells.csv` or `.json`): Complete per-cell metadata.
-- **CHANGELOG.md**: Record of updates and changes.
-- **License file** (`LICENSE.txt`): Specifies data usage terms.
-- **References**: Citations for methods, standards, and related publications.
----
-### 6. Tools for Metadata Preparation and Validation
-- [ISA-Tab tools](https://isa-tools.org/) (for structured experimental metadata)
-- [FAIRshake](https://fairshake.cloud/) (for FAIRness assessment)
-- [BioSamples Validator](https://www.ebi.ac.uk/biosamples/docs/api/validators) (for sample metadata)
-- [NIMH Data Archive (NDA) Validation Tools](https://nda.nih.gov/tools/validation.html) (if submitting to NDA)
-- [DataCite Metadata Generator](https://datacite.org/tools.html) (for DOI metadata)
----
-### 7. De-identification and Privacy Considerations
-- **Current study (mouse data):**  
-  - **No de-identification required** as no human subjects are involved.
-  - Ensure that metadata does not inadvertently include any sensitive or proprietary information.
-- **Future human data:**  
-  - **De-identification will be required** if/when human data are included.
-  - Follow NIH and NIMH policies for human data sharing, including removal of direct and indirect identifiers.
-  - Ensure consent language permits data sharing at the intended level; update data sharing plans and repository selection accordingly.
----
-### 8. Recommended Repositories
-- **Primary recommendation:**  
-  - [NeMO Archive](https://nemoarchive.org/) – NIH-supported, domain-specific for neuroscience multi-omic data.
-- **Alternatives:**  
-  - [Gene Expression Omnibus (GEO)](https://www.ncbi.nlm.nih.gov/geo/) – widely used for genomics and transcriptomics.
-  - [Synapse](https://www.synapse.org/) – NIMH/NIH-recommended, supports multi-modal data and metadata.
-  - [EBI ArrayExpress](https://www.ebi.ac.uk/arrayexpress/) – for transcriptomics data.
-- **For future human data:**  
-  - [NIMH Data Archive (NDA)](https://nda.nih.gov/) – required for certain human data types.
----
-### 9. Recommended Data Licenses
-- **Recommended license:**  
-  - **Creative Commons Attribution 4.0 International (CC BY 4.0)** – maximizes reuse and is NIH/NIMH recommended for non-human data.
-- **If restrictions apply (future human data):**  
-  - License and access level must comply with consent language and NIH/NIMH policies; consider **controlled access** if required.
-- **Include a `LICENSE.txt` file** specifying the chosen license.
----
-**Summary:**  
-By following these FAIR data practices—using open formats, community standards, robust metadata, and NIH-recommended repositories—your dataset will be well-positioned for maximum findability, accessibility, interoperability, and reuse, in line with NIMH and NIH expectations. Update your data sharing plan as needed if human data are added in the future.</t>
+          <t>Certainly! Below is practical, NIH/NIMH-tailored FAIR data guidance for your spatially mapped single-cell mouse brain atlas project, organized by the requested sections.
+---
+### 1. Suggested file formats for each data type
+**Single-cell matrices (counts, UMIs, methylation):**
+- **Matrix Market (.mtx)**: Widely used for sparse matrices in single-cell genomics; open, interoperable, and supported by major analysis tools.
+- **HDF5-based formats (.h5ad for AnnData, .loom, .h5)**: Efficient for large datasets, support complex metadata, and are compatible with popular single-cell analysis platforms (Scanpy, Seurat).
+- **CSV/TSV**: For smaller or summary tables; universally readable but less efficient for large, sparse data.
+**Metadata tables:**
+- **CSV/TSV**: Human- and machine-readable, widely supported, and suitable for tabular metadata.
+**Spatial coordinates and images:**
+- **CSV/TSV**: For coordinate tables.
+- **OME-TIFF**: For microscopy images; open standard for bioimaging, supports metadata embedding.
+**Why:** These formats are open, well-documented, widely adopted in the single-cell and neuroscience communities, and facilitate interoperability and long-term preservation.
+---
+### 2. Tools for converting data to the suggested file formats
+- **Seurat (R)**: Export to .mtx, .csv, .loom, .h5ad.
+- **Scanpy (Python)**: Export to .h5ad, .mtx, .csv.
+- **Loompy**: For .loom file creation.
+- **Cell Ranger (10x Genomics)**: Outputs .mtx and .csv by default.
+- **Custom scripts (R/Python)**: For format conversion as needed.
+- **Bio-Formats**: For converting microscopy images to OME-TIFF.
+---
+### 3. Suggested standard structure to organize the dataset
+**Recommended approach:**  
+Adopt the **OpenNeuro BIDS-inspired structure** for single-cell data, or the **Single Cell Expression Atlas (SCEA) guidelines**:
+- **/raw/**: Raw data (e.g., FASTQ, raw images)
+- **/processed/**: Processed matrices (.mtx, .h5ad, .loom), metadata tables
+- **/metadata/**: Data dictionaries, README, protocols
+- **/code/**: Analysis scripts, pipelines
+- **/docs/**: Publications, supplementary materials
+**If spatial transcriptomics:** Consider the **Spatial Omics Imaging Data Structure (SOI-DS)**, an extension of BIDS for spatial omics.
+---
+### 4. Tools for organizing the dataset in the suggested structure
+- **BIDS Starter Kit**: Templates and checklists for BIDS-like organization.
+- **SCEA submission templates**: For Single Cell Expression Atlas structure.
+- **OpenNeuro tools**: For BIDS validation (adapt as needed).
+- **Custom scripts**: For folder and file organization.
+- **Git/GitHub**: For version control of code and documentation.
+---
+### 5. Metadata and information that should be provided with the data
+- **Project-level README**: Overview, data types, file descriptions, contact info.
+- **Data dictionary/codebook**: Definitions for all variables/columns in metadata tables.
+- **Experimental protocols**: Detailed sample prep, sequencing, and processing steps (can reference protocols.io).
+- **Provenance information**: Software versions, pipeline parameters, QC metrics.
+- **Sample metadata**: Animal sex, developmental time point, punch origin (x,y,z), cluster/subcluster assignments, QC metrics, sequencing platform, preparation dates, etc.
+- **Data processing workflow**: Description or scripts for data processing and analysis.
+- **Citations and funding acknowledgments**.
+---
+### 6. Suggested standard structure and file format for metadata
+- **Format:**  
+  - **CSV/TSV**: For tabular sample/cell metadata.
+  - **YAML/JSON**: For project-level metadata (machine-readable, supports nesting).
+  - **README.md (Markdown)**: For human-readable documentation.
+- **Structure:**  
+  - **MINSEQE** (Minimum Information about a High-Throughput Nucleotide Sequencing Experiment) for sequencing metadata.
+  - **MIAME** (for microarray, if relevant).
+  - **SCEA metadata schema**: For single-cell experiments.
+  - **BIDS-style dataset_description.json**: For project-level metadata.
+---
+### 7. Tools for preparing metadata in the suggested structure and file format
+- **SCEA metadata templates**: For sample and experiment metadata.
+- **BIDS Validator**: For checking BIDS-like structure (adapt for single-cell).
+- **ISA-Tab tools**: For structured metadata (ISAcreator, ISA-tools).
+- **Excel/Google Sheets**: For preparing CSV/TSV metadata tables.
+- **YAML/JSON editors**: For project-level metadata.
+- **protocols.io**: For protocol documentation and sharing.
+---
+### 8. Suggested de-identification approach
+**Not required for mouse data:**  
+Since the dataset is derived from non-human (mouse) subjects, de-identification is not required.  
+**If/when human data are included:**  
+- Remove all direct and indirect identifiers (e.g., names, dates of birth, unique codes linked to individuals).
+- Aggregate or generalize sensitive metadata (e.g., age ranges, broad location).
+- Ensure compliance with consent language and NIH Genomic Data Sharing Policy.
+---
+### 9. Tools to implement the suggested de-identification approach
+- **Custom scripts**: For removing or masking sensitive fields in metadata.
+- **DeID (R package)**: For de-identification of tabular data (if human data are included).
+- **Manual review**: To ensure no indirect identifiers remain.
+---
+### 10. Suggested repositories for sharing the dataset
+**Recommended approach:**  
+- **Gene Expression Omnibus (GEO)**: NIH-recommended, widely used for single-cell and spatial genomics data.
+- **Single Cell Expression Atlas (EMBL-EBI)**: For single-cell RNA-seq and multi-omics data.
+- **NeuroMorpho.Org**: For spatial/structural data (if relevant).
+- **OpenNeuro**: For BIDS-structured datasets (if spatial imaging is a major component).
+- **NIMH Data Archive (NDA)**: If required by NIMH or if human data are included in the future.
+---
+### 11. Suggested license for sharing the dataset
+**Recommended approach:**  
+- **CC BY 4.0 (Creative Commons Attribution 4.0 International)**: NIH and NIMH encourage open sharing with attribution; this license maximizes reuse while ensuring credit.
+- **If human data are included and consent restricts sharing:**  
+  - Use controlled access (e.g., dbGaP, NDA) and specify data use limitations as required by consent.
+---
+**Summary Table**
+| Section | Recommendation |
+|---------|---------------|
+| File formats | .mtx, .h5ad, .loom, .csv/.tsv, OME-TIFF |
+| Conversion tools | Seurat, Scanpy, Loompy, Cell Ranger, Bio-Formats |
+| Dataset structure | BIDS-inspired or SCEA guidelines |
+| Organization tools | BIDS Starter Kit, SCEA templates, GitHub |
+| Metadata to provide | README, data dictionary, protocols, provenance, sample metadata |
+| Metadata format | CSV/TSV, YAML/JSON, README.md, MINSEQE, SCEA schema |
+| Metadata tools | SCEA templates, BIDS Validator, ISA-Tab tools, protocols.io |
+| De-identification | Not required for mouse; follow NIH policy for human data |
+| De-ID tools | Custom scripts, DeID (if human data) |
+| Repositories | GEO, SCEA, OpenNeuro, NDA (if human data) |
+| License | CC BY 4.0 (unless restricted by consent) |
+---
+**References:**
+- NIH Genomic Data Sharing Policy: https://grants.nih.gov/grants/guide/notice-files/NOT-OD-14-124.html
+- NIMH Data Sharing Policy: https://www.nimh.nih.gov/funding/grant-writing-and-application-process/data-sharing-and-management
+- SCEA submission guidelines: https://www.ebi.ac.uk/gxa/sc/experiments
+- BIDS: https://bids.neuroimaging.io/
+- OME-TIFF: https://www.openmicroscopy.org/ome-model/ome-tiff/
+---
+**If you need templates, example metadata files, or further clarification for any section, please let me know.**</t>
         </is>
       </c>
     </row>
@@ -1077,24 +1090,28 @@
  be uploaded to NDA during the second quarter of the first year of funding. As discussed in the application, 
  structural MRI scans are available for time points before and after treatment along with relevant clinical data.
 Based on these inputs, provide clear, practical, and user-friendly FAIR data guidance organized under the following sections:
-1. Recommended file formats  
-Explain which file format(s) should be used for this type of data and why they are appropriate for FAIR sharing and reuse.
-2. Relevant tools and software  
-List tools, software, or platforms that can help prepare, convert, validate, organize, document, or share this type of data.
-3. Recommended dataset structure or standard  
-State the dataset structure, schema, or community standard that should be followed, if one exists.
-4. Dataset organization details  
-Provide detailed guidance on how the dataset should be organized, including folder structure, file naming conventions, table organization, metadata arrangement, versioning considerations, and any other important technical details.
-5. Metadata and documentation files to include  
-List the metadata files, README files, data dictionaries, codebooks, protocols, or other documentation that should accompany the dataset.
-6. Tools for metadata preparation and validation  
-Suggest tools that can help create, validate, manage, or standardize metadata for this dataset.
-7. De-identification and privacy considerations  
-State whether de-identification is required. Explain what should be done based on the subject type, the data modality, and whether the study involves human participants. If consent language affects sharing, explain that clearly.
-8. Recommended repositories  
-Suggest appropriate repositories for sharing the data, prioritizing repositories recommended, required, or commonly accepted by the funding source and data type.
-9. Recommended data licenses  
-Recommend appropriate data license(s), prioritizing those expected, suggested, or required by the funding source. If restrictions apply because of human subjects or consent limitations, explain that clearly.
+1- Suggested file formats for each data type
+Identify the recommended file format or formats for each data type in the dataset. Briefly explain why these formats are appropriate for FAIR sharing, reuse, interoperability, and long-term preservation.
+2- Tools for converting data to the suggested file formats
+List tools, software, or workflows that can be used to convert raw or source data into the recommended file formats.
+3- Suggested standard structure to organize the dataset
+State the recommended dataset structure, schema, specification, or community standard that should be used to organize the dataset, if one exists.
+4- Tools for organizing the dataset in the suggested structure
+List tools, software, templates, or platforms that can help organize the dataset according to the recommended structure or standard.
+5- Metadata and information that should be provided with the data
+Describe the metadata, documentation, contextual information, data dictionaries, codebooks, README files, protocols, and any other supporting information that should accompany the dataset.
+6- Suggested standard structure and file format for metadata
+State the recommended structure, schema, standard, and file format that should be used for metadata and documentation files included with the dataset.
+7-Tools for preparing metadata in the suggested structure and file format
+List tools, software, validators, templates, or platforms that can help create, manage, standardize, or validate metadata in the recommended structure and format.
+8- Suggested de-identification approach
+State whether de-identification is required. Explain the recommended de-identification or privacy-preserving approach based on the subject type, data modality, sensitivity of the data, and whether human participants are involved. If consent language affects sharing, explain that clearly.
+9- Tools to implement the suggested de-identification approach
+List tools, software, workflows, or methods that can help implement the recommended de-identification or privacy protection approach.
+10-Suggested repositories for sharing the dataset
+Recommend appropriate repositories for sharing the dataset, prioritizing repositories required, recommended, or commonly accepted by the funding source, subject type, and data modality.
+11- Suggested license for sharing the dataset
+Recommend an appropriate data license or licensing approach, prioritizing what is expected, suggested, or required by the funding source. If restrictions apply because of human subjects, controlled access, or consent limitations, explain that clearly.
 Instructions for your response:
 - Make the guidance practical, concise, and easy for researchers to follow.
 - Tailor all recommendations to the combination of funding source, human-subject status, consent language, and data modality.
@@ -1106,113 +1123,89 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Certainly! Below is practical, NIH/NIMH-tailored FAIR data guidance for your grant proposal involving human MRI and clinical assessment data.
----
-## 1. Recommended File Formats
+          <t>**FAIR Data Guidance for NIH/NIMH Human Subjects MRI and Clinical Assessment Data**
+---
+### 1. Suggested file formats for each data type
 **MRI Images:**  
-- **NIfTI (.nii or .nii.gz):** The Neuroimaging Informatics Technology Initiative (NIfTI) format is the community standard for MRI data. It is open, widely supported, and required by the NIMH Data Archive (NDA).
-- **DICOM (.dcm):** If raw scanner output is needed, DICOM is acceptable, but NIfTI is preferred for sharing and analysis.
+- **Format:** NIfTI (.nii or .nii.gz)  
+- **Rationale:** NIfTI is the community standard for neuroimaging, widely supported, open, and ensures interoperability and long-term preservation.
 **Clinical Assessments:**  
-- **Tabular Data:** Use non-proprietary, machine-readable formats such as **CSV (.csv)** or **TSV (.tsv)**. Avoid Excel (.xls/.xlsx) for primary data sharing.
-- **Textual Documentation:** Use **PDF (.pdf)**, **Markdown (.md)**, or **plain text (.txt)** for protocols, README files, and codebooks.
----
-## 2. Relevant Tools and Software
-- **BIDS Validator:** For checking compliance with the BIDS standard (see below).
-- **dcm2niix:** For converting DICOM MRI files to NIfTI.
-- **HeuDiConv:** For automated DICOM-to-BIDS conversion.
-- **NDA Data Uploader:** For submitting data to the NIMH Data Archive.
-- **REDCap, OpenClinica, or similar:** For organizing and exporting clinical assessment data.
-- **DataLad or Git:** For version control and dataset management.
-- **OpenNeuro Tools:** For BIDS dataset preparation and validation.
----
-## 3. Recommended Dataset Structure or Standard
-- **MRI Data:**  
-  Follow the **Brain Imaging Data Structure (BIDS)** standard (https://bids.neuroimaging.io/), which is widely adopted for neuroimaging data and required by many repositories, including NDA and OpenNeuro.
-- **Clinical Data:**  
-  Organize according to BIDS “phenotype” conventions or NDA data dictionary templates. Use consistent variable names and coding.
----
-## 4. Dataset Organization Details
-- **Folder Structure:**  
-  ```
-  /project_root/
-    /sub-&lt;participant_id&gt;/
-      /ses-&lt;session_id&gt;/
-        /anat/         # Structural MRI (e.g., T1w)
-          sub-&lt;id&gt;_ses-&lt;id&gt;_T1w.nii.gz
-        /func/         # Functional MRI (if any)
-        /dwi/          # Diffusion MRI (if any)
-    /phenotype/
-      participants.tsv
-      clinical_assessments.tsv
-    /code/
-      analysis_scripts/
-    /docs/
-      README.md
-      dataset_description.json
-      CHANGES.md
-      data_dictionary.csv
-      protocol.pdf
-  ```
-- **File Naming:**  
-  Use BIDS conventions: `sub-&lt;participant_id&gt;_ses-&lt;session_id&gt;_&lt;modality&gt;.nii.gz`
-- **Tabular Data:**  
-  - Each row = one participant or assessment.
-  - Columns = variables, with clear, consistent names.
-- **Metadata Arrangement:**  
-  - Place `dataset_description.json` at the root.
-  - Include `participants.tsv` and any other key tables in `/phenotype/`.
-  - Document all variables in a data dictionary.
-- **Versioning:**  
-  - Use version numbers in `dataset_description.json` and maintain a `CHANGES.md` log.
-  - Consider using Git or DataLad for tracking changes.
----
-## 5. Metadata and Documentation Files to Include
-- **README.md:** Overview of dataset, structure, and usage.
-- **dataset_description.json:** Required by BIDS; describes dataset, authors, funding, ethics, etc.
-- **participants.tsv:** Participant-level metadata (age, sex, diagnosis, etc.).
-- **data_dictionary.csv:** Definitions and coding for all variables in tabular data.
-- **CHANGES.md:** Version history and updates.
-- **protocol.pdf:** Study protocol and data collection procedures.
-- **Consent documentation:** Template or summary of consent language (if allowed).
-- **Codebooks:** For clinical assessments, if not included in data dictionary.
----
-## 6. Tools for Metadata Preparation and Validation
-- **BIDS Validator:** (https://bids-standard.github.io/bids-validator/)
-- **NDA Data Dictionary Tools:** For preparing NDA-compliant metadata.
-- **OpenNeuro Metadata Tools:** For BIDS metadata.
-- **DataLad:** For metadata management and provenance tracking.
-- **REDCap Data Dictionary Export:** For clinical data.
----
-## 7. De-identification and Privacy Considerations
-- **De-identification is required** for all human subject data prior to sharing.
-- **MRI Data:**  
-  - Remove all facial features from structural MRI scans (defacing) using tools like `pydeface` or `mri_deface`.
-  - Strip all personal identifiers from DICOM headers.
-- **Clinical Data:**  
-  - Remove direct identifiers (names, addresses, dates of birth, etc.).
-  - Use only study-specific participant IDs.
-- **Consent:**  
-  - All participants are consented for broad data sharing, which supports open sharing in repositories like NDA.
-  - Ensure that shared data and documentation do not contain any information that could re-identify participants.
----
-## 8. Recommended Repositories
-- **Primary:**  
-  - **NIMH Data Archive (NDA):** Required and preferred for NIMH-funded human neuroimaging and clinical data. NDA supports BIDS and provides controlled access for sensitive data.
-- **Secondary (if appropriate):**  
-  - **OpenNeuro:** For BIDS-compliant, de-identified neuroimaging datasets, if additional open sharing is desired and allowed by consent.
-  - **Other NIH-supported repositories:** Only if NDA is not suitable, but NDA is the standard for NIMH.
----
-## 9. Recommended Data Licenses
-- **NDA Data Use Terms:**  
-  - Data shared via NDA is governed by NDA’s Data Use Certification Agreement, which ensures responsible use and compliance with participant consent.
-  - No additional license is typically required; NDA’s terms are sufficient and appropriate for human subject data.
-- **If sharing on OpenNeuro:**  
-  - Use the **Creative Commons CC0** waiver for de-identified data, unless participant consent or institutional policy requires more restrictive terms.
-- **Note:**  
-  - For human subject data, always ensure that the chosen license or data use agreement aligns with the consent provided by participants and institutional review board (IRB) requirements.
+- **Format:** CSV (.csv) or TSV (.tsv)  
+- **Rationale:** Plain text tabular formats are non-proprietary, machine-readable, and maximize reuse and interoperability.
+**Supporting Documentation (e.g., protocols, codebooks):**  
+- **Format:** PDF (.pdf), Markdown (.md), or plain text (.txt)  
+- **Rationale:** These formats are open, widely accessible, and suitable for long-term preservation.
+---
+### 2. Tools for converting data to the suggested file formats
+**MRI Images:**  
+- **dcm2niix:** Converts DICOM to NIfTI format.  
+- **MRIcron/MRIconvert:** GUI tools for DICOM to NIfTI conversion.
+**Clinical Assessments:**  
+- **Spreadsheet software (Excel, LibreOffice Calc):** Export data as CSV/TSV.  
+- **R, Python (pandas):** For programmatic conversion and cleaning.
+**Documentation:**  
+- **Word processors (MS Word, Google Docs):** Export as PDF or plain text.  
+- **Markdown editors (Typora, VS Code):** For .md files.
+---
+### 3. Suggested standard structure to organize the dataset
+**Recommended:**  
+- **BIDS (Brain Imaging Data Structure)** for MRI and associated behavioral/clinical data.
+**Rationale:**  
+BIDS is the widely adopted community standard for organizing neuroimaging datasets, facilitating interoperability, reuse, and compliance with repository requirements (including NDA).
+---
+### 4. Tools for organizing the dataset in the suggested structure
+- **BIDS Starter Kit:** Templates and guides for BIDS organization.
+- **HeuDiConv:** Automated DICOM-to-BIDS conversion.
+- **BIDScoin:** GUI tool for converting and organizing data into BIDS.
+- **NDA Data Dictionary Tools:** For aligning clinical data with NDA requirements.
+---
+### 5. Metadata and information that should be provided with the data
+- **Dataset-level README:** Overview, study purpose, data collection methods, and contact information.
+- **Data dictionary/codebook:** Definitions, allowable values, and descriptions for all variables.
+- **Protocol documentation:** Detailed data collection and processing protocols.
+- **BIDS metadata files:** `dataset_description.json`, `participants.tsv`, and modality-specific JSON sidecars.
+- **Consent documentation:** Summary of consent language regarding data sharing.
+- **Provenance information:** Data processing steps, software versions, and quality control procedures.
+---
+### 6. Suggested standard structure and file format for metadata
+- **BIDS JSON sidecar files:** For MRI and behavioral data metadata.
+- **NDA Data Dictionary format:** For clinical/phenotypic data (CSV/TSV with accompanying data dictionary).
+- **README and codebooks:** Plain text (.txt), Markdown (.md), or PDF (.pdf).
+---
+### 7. Tools for preparing metadata in the suggested structure and file format
+- **BIDS Validator:** Checks compliance with BIDS structure and metadata.
+- **BIDS Starter Kit templates:** For metadata files.
+- **NDA Data Dictionary Tool:** For preparing NDA-compliant data dictionaries.
+- **Spreadsheet software:** For creating data dictionaries and codebooks.
+- **JSON editors (e.g., Visual Studio Code):** For editing BIDS JSON files.
+---
+### 8. Suggested de-identification approach
+**Required:**  
+Yes, de-identification is required for all human subjects data.
+**Recommended approach:**  
+- **MRI Images:** Remove all facial features (defacing) and all direct identifiers from image headers (e.g., name, date of birth, study dates).
+- **Clinical Assessments:** Remove or code all direct identifiers (names, addresses, dates of birth, etc.) and use study-specific participant IDs.
+- **Consent:** As all participants are consented for broad data sharing, data can be shared via controlled-access repositories (e.g., NDA) following NIH/NIMH policy.
+---
+### 9. Tools to implement the suggested de-identification approach
+- **pydeface, mri_deface, or fsl_deface:** For defacing MRI images.
+- **DICOM anonymization tools (e.g., DicomCleaner):** For removing identifiers from DICOM headers before conversion.
+- **Custom scripts (Python, R):** For removing identifiers from clinical data.
+- **NDA Data Validation Tools:** For checking compliance with NDA de-identification requirements.
+---
+### 10. Suggested repositories for sharing the dataset
+**Required/Recommended:**  
+- **NIMH Data Archive (NDA):**  
+  - **Rationale:** NDA is the NIH/NIMH-mandated repository for human subjects neuroimaging and clinical data. It supports controlled access, aligns with NIH data sharing policy, and is already used for your existing collections.
+---
+### 11. Suggested license for sharing the dataset
+**Recommended:**  
+- **NDA Data Use Certification (DUC):**  
+  - **Rationale:** NDA data are shared under controlled access with a Data Use Certification, in accordance with NIH policy and participant consent for broad sharing.  
+  - **Note:** Data will not be openly licensed (e.g., CC BY) but will be available to qualified researchers under NDA’s controlled access terms, consistent with human subjects protections and consent.
 ---
 **Summary:**  
-By following these recommendations—using BIDS and NDA standards, open formats, robust metadata, and strict de-identification—you will maximize the FAIRness, compliance, and reusability of your MRI and clinical assessment data in line with NIH/NIMH expectations.</t>
+By following these recommendations—using open, community-accepted formats (NIfTI, CSV/TSV), organizing data with BIDS, providing comprehensive metadata, de-identifying all human subjects data, and depositing in NDA under controlled access—you will ensure your data are maximally FAIR, compliant with NIH/NIMH policy, and reusable by the research community.</t>
         </is>
       </c>
     </row>
